--- a/execution/a902-s01-kyoto-ink-20261026/S16_GYARTAS/40_F3F4_dokumentacio/S16_R15B_szabasjegyzek.xlsx
+++ b/execution/a902-s01-kyoto-ink-20261026/S16_GYARTAS/40_F3F4_dokumentacio/S16_R15B_szabasjegyzek.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Vasalat" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Furatok" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Nyitott és jelmagyarázat" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Anyagjavaslat" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="920">
   <si>
     <t xml:space="preserve">Címke-ID (MPR alap)</t>
   </si>
@@ -2485,6 +2486,355 @@
   </si>
   <si>
     <t xml:space="preserve">Lapanyag/dekor termék és táblaméret; élzáró vastagság és előmarás; polctartó típus; fiók sín furatképe; LED-profilok; helyszíni felmérés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anyagkód</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gyártó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termékkód</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Név</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felület</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Táblaméret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élzáró (ABS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forgalmazó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ár</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ár egység / megjegyzés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ár dátuma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Színegyezés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U741 ST9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lava Grey / Láva szürke (Eurodekor laminált forgácslap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST9 Smoothtouch Matt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2800x2070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS E_U741 ST9 – 0,8/23 mm (JAF cikksz. 24744/0741) vagy 2/23 mm (24721/0741)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapp-fa Kft. (Budapest XVII. ker. telephely, készleten) / Fabuli Style / JAF Holz Hungária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla nettó (Lapp-fa); Fabuli: 37 764 nettó / 47 960 bruttó/tábla; Fabuli él 0,8/23: 230 Ft bruttó (egység nincs kiírva, valószínűleg fm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: Egger saját referenciája NCS S 7005-Y20R (nagyon jó egyezés), RAL 7013 – meleg, vöröses grafit; #504942-höz a legközelebbi talált uni. 1 mm-es Egger ABS ehhez a dekorhoz nem látszott a forrásokban (csak 0,4/0,8/2 mm) – 0,8 vagy 2 mm-re kell dönteni, vagy Rehau/Ostermann 1 mm-es párost kérni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lapp-fa.hu/butorlap/u-741-st9-lava-szurke-18mm-2800x2070-154.html
+https://fabuli.hu/butorlap-egger-uni-u741-st9-lava-szurke-2800x2070x18mm-7646
+https://www.jafholz.hu/shop/Dekorativ-lapok/Laminalt-forgacslap/egger-eurodekor-laminalt-forgacslap-lava-szurke-u741-st9~p2204155
+https://www.egger.com/en/interior/decor-detail/U741_9?country=GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAVASLAT – mintával ellenőrizendő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U748 ST9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truffle Brown / Trüffel barna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS E_U748 ST9 – 0,8/23 mm vagy 2,0/23 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapp-fa Kft. (készleten mindhárom telephelyen) / Fabuli Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla nettó (Lapp-fa); Fabuli: 33 819 nettó / 42 950 bruttó/tábla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: Egger ref. NCS S 7005-Y50R – barnább, mint a cél; csak akkor, ha a grafit helyett barnásabb korpusz kell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lapp-fa.hu/butorlap/u-748-st9-truffel-18mm-2800x2070-344.html
+https://fabuli.hu/butorlap-egger-uni-u748-st9-truffel-barna-2800x2070x18mm-7647
+https://www.egger.com/en/interior/decor-detail/U748_9?country=GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger (hordozó) + IVM Chemicals / Milesi (festékrendszer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger MDF natúr 18 mm + Milesi LBR 30 2K PU fehér MDF-alapozó (edző LNB 42, 50%) + Milesi PU pigmentált fedőfesték szatén fokban, NCS-re keverve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szatén sötét barnásgrafit festett MDF keret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2K PU, szatén (fényfok a festékrendszer adatlapja szerint, pl. 20–30 gloss – egyeztetendő)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDF: Lapp-fa Kft. (a forrás szerint jelenleg nincs készleten); festék: M.L.S. Magyarország Kft. (Milesi HU, 2310 Szigetszentmiklós, Sellő u. 8.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla (MDF) nettó; festék ár nincs nyilvános</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szín becslés #332c26-ra: NCS S 8005-Y50R körül; RAL közelítés RAL 8019 (Szürkésbarna) – mindkettő saját becslés, nem gyártói adat. Festett minta (drawdown) MDF-en kötelező. A szatén fedőfesték pontos Milesi-cikkszáma a forgalmazótól kérendő (nyilvánosan nem találtam).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lapp-fa.hu/mdf/mdf-egger-natur-18mm-2800x2070-141.html
+https://www.milesi.hu/ipari-felhasznalok/component/pes/product/66?catid=2212
+https://milesi.hu/lakossagi-felhasznalok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayerlack (Sherwin-Williams) festékrendszer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sayerlack 2K PU pigmentált alapozó + fedő, NCS-re színezve – cikkszám a forgalmazótól</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternatív festékrendszer ugyanarra az Egger MDF 18 mm hordozóra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2K PU szatén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mile Color Kft. (Sayerlack HU szerződött partner, Miskolc) / Lakgruppen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ár nincs nyilvános; termékkód nem látszott a forrásban – csak a márka és forgalmazó igazolt. Az asztalos/fényező saját bevált rendszere is elfogadható, ha NCS-mintát ad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sayerlack.hu/
+https://lakgruppen.hu/sayerlack/b/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1399 ST10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truffle Brown Denver Oak / Trüffel barna Denver tölgy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST10 Deepskin Rough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS H1399 ST10 (0,8 vagy 2 mm; pontos cikkszám a forgalmazótól)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapp-fa Kft. (készleten mindhárom telephelyen) / Fabuli / Szabhatjuk.hu (1037 Bp., Csillaghegyi út 23.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla nettó (Lapp-fa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: Egger leírás szerint barna, meleg és hideg tónusok keveréke, finom erezet, kis görcsök, enyhe deszkahatás – a 'füstös barnásszürke' célhoz (#40362e) közel, de görcsös. Erezetirány: tábla hossza 2800 mm mentén fut; magas ajtók függőleges erezetéhez 2800 mm-es irány elég, vízszintes frontoknál a szabásterv ezt vegye figyelembe. Az ABS élhez az ST10 dekorpárt a forgalmazó erősítse meg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lapp-fa.hu/butorlap/h-1399-st10-truffelbarna-denver-tolgy-18mm-2800x2070-672.html
+https://szabhatjuk.hu/termek/egger-h1399-st10-truffel-barna-denver-tolgy-butorlap/
+https://www.egger.com/en/interior/decor-detail/H1399_10?country=GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1199 ST12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black-Brown Thermo Oak / Sötétbarna Thermo tölgy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST12 Omnipore Matt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS H1199 ST12 – 0,8/23 mm vagy 2,0/23 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabuli Style (központi raktár, várható 2026-11-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla bruttó (Fabuli; nettó 37 764); él 0,8/23: 290 Ft bruttó, 2,0/23: 400 Ft bruttó (egység nincs kiírva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: sötétebb, kevésbé szürke, mint a cél; nyugodtabb, görcs nélküli 'thermo' karakter. Szín-referenciát (NCS) nem találtam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fabuli.hu/butorlap-egger-fautanzat-h1199-st12-sotetbarna-thermo-tolgy-2800x2070x18mm-7690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U740 ST9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Taupe / Sötét taupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST9 Smoothtouch Matt (NEM textilhatású)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS U740 ST9 (cikkszám a forgalmazótól)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szabhatjuk.hu (Budapest) – ár nem látszott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ár nincs nyilvános. Becslés: Egger ref. NCS S 5005-Y20R – színben a legközelebbi talált meleg taupe a #706252-höz (a cél kissé sárgásabb/telítettebb), de a felület sima matt, nem textil. Ha a textilhatás fontosabb, lásd 2. jelölt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://szabhatjuk.hu/termek/sotet-taupe-butorlap-egger-u740-st9/
+https://www.egger.com/en/interior/decor-detail/U740_9?country=GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F416 ST10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Textile / Bézs textil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST10 Deepskin Rough – textil/szövet struktúra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS E_F416 ST10 – 0,8/23 mm vagy 2,0/23 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabuli Style (központi raktár, várható 2026-11-10) / JAF Holz / Szabhatjuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla bruttó (Fabuli; nettó 35 457); él 0,8/23: 280 Ft, 2,0/23: 400 Ft bruttó (egység nincs kiírva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: valódi textilhatás, de valószínűleg VILÁGOSABB a #706252-nél (NCS-ref. nem található) – csak mintával dönthető el. Sötét textil-alternatíva: Egger F433 ST10 Antracit len (túl hideg/sötét a célhoz).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fabuli.hu/butorlap-egger-fantazia-f416-st10-bezs-textil-2800x2070x18mm-7761
+https://www.jafholz.hu/shop/lap--lemez-termekek/dekorativ-lap/laminalt-forgacslap/egger-laminalt-forgacslap-textil-bezs-f416-st10~p6939089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kvadrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallingdal 65, szín 0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallingdal 65 – bézs/törtfehér melírozott gyapjú kárpitszövet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szövött, 70% új gyapjú / 30% viszkóz, Martindale 100 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tekercs, szélesség 1300 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magyar Kvadrat-viszonteladó: paisley.hu (Kvadrat kollekciókat listáz; Hallingdal HU-készlet nem igazolt) – EU-webshop: etoffe.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR/fm nincs jelölve (etoffe.com, FR; jelenleg nincs készleten)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becslés: 0200 = bézs és törtfehér szálak keveréke – elefántcsont–len (#c7bca7) hangulathoz illik, pontos árnyalat csak mintával (Kvadrat minta ~4 EUR). Magyar ár nincs nyilvános. Kvadrat 0110 is jelölt lehet, adatát nem tudtam ellenőrizni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://audocph.com/collections/hallingdal-65/products/hallingdal-65-0200
+https://www.etoffe.com/en/furnishing-fabrics/11771-hallingdal-65-fabric-kvadrat.html
+https://paisley.hu/kollekciok/fuggony-butorszovet-kollekciok/kvadrat-textil/kvadrat-san-0910-karpit-anyag-butorszovet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ismeretlen (finn/balti nyír, gyártó nincs megnevezve a forrásban)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nyír rétegelt lemez 15 mm BB/WG, BFU-100 (DIN 68705), 11 réteg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nyír rétegelt lemez fiókdobozhoz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mindkét oldal javított, csiszolt; matt vízbázisú lakk külön</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2500x1250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKFT Faáruház (6750 Algyő; webes rendelés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ft/tábla nincs jelölve a forrásban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Látszó él (rétegzett nyír) – az élminőséget (hézag, foltok) mintával/első táblánál ellenőrizni. Gyártó (pl. Riga Wood/Koskisen) nem igazolt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.okftfaaruhaz.hu/NYIR-RET-LEM-15mm-BB/WG-vizallo-2500x1250x15mm-BFU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U961 ST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphite Grey – 8 mm kétoldalt melaminos forgácslap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST2 Smoothtouch Pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HU: nem találtam raktári 8 mm-es tételt (Fabuli a 18 mm-es U961 ST2-t 'NEM KAPHATÓ'-nak jelöli); Forest Hungary U961 ST7 18 mm-t listáz – 8 mm csak rendelésre, ellenőrizendő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ár nincs nyilvános (HU). A 8 mm-es U961 ST2 létezése csak brit forgalmazónál látszott. Szín becslés: U961 valószínűleg sötétebb és hidegebb a #696c67-nél.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lawcris.co.uk/2800mm-x-2070mm-x-8mm-u961-st2-graphite-grey-melamine-faced-chipboard-cmeu961st208
+https://fabuli.hu/butorlap-egger-uni-u961-st2-grafit-szurke-2800x2070x18mm-7663
+https://www.foresteu.com/laptermekek-es-tartozekaik/butorlap/egger-uni/20010961182-butorlap-egger-uni-u961-st7-grafit-szurke-2800x2070x18mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U963 ST9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond Grey / Gyémántszürke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16, 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger · ABS U963 ST9 – 0,8/23 mm (JAF 24744/0963)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAF Holz Hungária (16 mm: 13113/0963; 18 mm: 13198/0963)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ár nincs nyilvános (JAF bejelentkezéshez köti). ELTÉRÉS: 8 mm helyett 16 mm – csak akkor, ha a hátlap-horony/szerkezet átírható; HU-ban 8 mm-ben nem látszott. Szín becslés: középgrafit, a #696c67-hez valószínűleg közelebb, mint az U961.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.jafholz.hu/shop/lap--lemez-termekek/dekorativ-lap/laminalt-forgacslap/egger-eurodekor-laminalt-forgacslap-gyemantszurke-u963-st9~p12239867</t>
   </si>
 </sst>
 </file>
@@ -2619,7 +2969,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2666,6 +3016,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -34869,4 +35223,655 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>29629</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>26534</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>21694</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>34950</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>47960</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>45030</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>38821</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>913</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>914</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>833</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>